--- a/Horarios2026.xlsx
+++ b/Horarios2026.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141A2A98-FB65-41B7-A4B2-6FBBD0DFBFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4CB16EAB-46E4-4296-9FB2-5DEE8DAED3CC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="TALLER1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="11">
   <si>
     <t>DESDE</t>
   </si>
@@ -56,11 +55,14 @@
   <si>
     <t>PRIMER CUATRIMESTRE</t>
   </si>
+  <si>
+    <t>SEGUNDO CUATRIMESTRE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -164,14 +166,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,39 +493,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB2B772-8170-4FFE-ABA1-AFA216428B0A}">
-  <dimension ref="B1:O42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="E1" s="5" t="s">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="E1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="L1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -546,37 +564,40 @@
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="6">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="5">
         <v>0.625</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>0.63194444444444442</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>0.63194444444444442</v>
       </c>
@@ -586,11 +607,14 @@
       <c r="D5">
         <v>2</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>0.63888888888888884</v>
       </c>
@@ -600,11 +624,14 @@
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>0.64583333333333304</v>
       </c>
@@ -614,11 +641,14 @@
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>0.65277777777777801</v>
       </c>
@@ -628,11 +658,14 @@
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>0.65972222222222199</v>
       </c>
@@ -642,11 +675,14 @@
       <c r="D9">
         <v>6</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>0.66666666666666696</v>
       </c>
@@ -656,11 +692,14 @@
       <c r="D10">
         <v>7</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>0.67361111111111105</v>
       </c>
@@ -670,25 +709,34 @@
       <c r="D11">
         <v>8</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="G11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>0.68055555555555503</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>0.6875</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>0.6875</v>
       </c>
@@ -698,14 +746,20 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>0.69444444444444398</v>
       </c>
@@ -715,14 +769,20 @@
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>0.70138888888888895</v>
       </c>
@@ -732,14 +792,20 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>0.70833333333333304</v>
       </c>
@@ -749,14 +815,20 @@
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>0.71527777777777701</v>
       </c>
@@ -766,14 +838,20 @@
       <c r="D17">
         <v>5</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>0.72222222222222199</v>
       </c>
@@ -783,31 +861,43 @@
       <c r="D18">
         <v>6</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
+      <c r="G18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
         <v>0.72916666666666596</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>0.73611111111111005</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>0.73611111111111105</v>
       </c>
@@ -817,22 +907,28 @@
       <c r="D20">
         <v>8</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>0.74305555555555503</v>
       </c>
       <c r="C21" s="1">
         <v>0.749999999999999</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>0.75</v>
       </c>
@@ -842,11 +938,14 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>0.75694444444444398</v>
       </c>
@@ -856,11 +955,14 @@
       <c r="D23">
         <v>2</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>0.76388888888888795</v>
       </c>
@@ -870,11 +972,14 @@
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>0.77083333333333304</v>
       </c>
@@ -884,11 +989,14 @@
       <c r="D25">
         <v>4</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>0.77777777777777701</v>
       </c>
@@ -898,25 +1006,31 @@
       <c r="D26">
         <v>5</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="8">
+      <c r="G26" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="7">
         <v>0.78472222222222199</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>0.79166666666666596</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>0.79166666666666596</v>
       </c>
@@ -927,7 +1041,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>0.79861111111111005</v>
       </c>
@@ -938,7 +1052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>0.80555555555555558</v>
       </c>
@@ -946,7 +1060,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>0.8125</v>
       </c>
@@ -954,7 +1068,7 @@
         <v>0.81944444444444442</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>0.81944444444444442</v>
       </c>
@@ -979,42 +1093,42 @@
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>0.84027777777777801</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>0.84722222222222199</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="7">
+      <c r="B36" s="6">
         <v>0.84722222222222221</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>0.85416666666666663</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="7">
+      <c r="B37" s="6">
         <v>0.85416666666666663</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>0.86111111111111005</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <v>0.86111111111111105</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="6">
         <v>0.86805555555555403</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <v>0.86805555555555503</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="6">
         <v>0.874999999999998</v>
       </c>
     </row>
@@ -1029,7 +1143,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="K1:O2"/>
+    <mergeCell ref="L1:P2"/>
     <mergeCell ref="E1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Horarios2026.xlsx
+++ b/Horarios2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE56DE57-6512-434A-91FA-744A5E69DC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TALLER1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="12">
   <si>
     <t>DESDE</t>
   </si>
@@ -58,11 +59,14 @@
   <si>
     <t>SEGUNDO CUATRIMESTRE</t>
   </si>
+  <si>
+    <t>NODO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -110,7 +114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,6 +151,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -160,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -168,12 +178,13 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -510,7 +521,7 @@
     <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.25">
@@ -593,8 +604,14 @@
       <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L4" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N4" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
@@ -610,8 +627,14 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L5" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N5" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
@@ -627,8 +650,14 @@
       <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L6" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N6" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
@@ -644,8 +673,14 @@
       <c r="G7" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L7" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N7" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
@@ -661,8 +696,14 @@
       <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L8" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N8" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
@@ -678,8 +719,14 @@
       <c r="G9" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L9" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N9" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
@@ -695,8 +742,14 @@
       <c r="G10" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L10" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N10" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
@@ -712,8 +765,14 @@
       <c r="G11" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="L11" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="N11" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">

--- a/Horarios2026.xlsx
+++ b/Horarios2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE56DE57-6512-434A-91FA-744A5E69DC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72799A34-9446-45D7-8AD3-412B7629CB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,7 +610,7 @@
       <c r="N4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="O4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -633,7 +633,7 @@
       <c r="N5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="O5" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -656,7 +656,7 @@
       <c r="N6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="O6" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="N7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="O7" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -702,7 +702,7 @@
       <c r="N8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="O8" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -725,7 +725,7 @@
       <c r="N9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="11" t="s">
+      <c r="O9" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -748,7 +748,7 @@
       <c r="N10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="O10" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -771,7 +771,7 @@
       <c r="N11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="O11" s="11" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Horarios2026.xlsx
+++ b/Horarios2026.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72799A34-9446-45D7-8AD3-412B7629CB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="TALLER1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="11">
   <si>
     <t>DESDE</t>
   </si>
@@ -59,14 +58,11 @@
   <si>
     <t>SEGUNDO CUATRIMESTRE</t>
   </si>
-  <si>
-    <t>NODO</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -181,10 +177,10 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,7 +500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -525,32 +521,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="L1" s="10" t="s">
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="L1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -604,15 +600,11 @@
       <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L4" s="10"/>
       <c r="N4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
@@ -627,15 +619,11 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L5" s="10"/>
       <c r="N5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O5" s="10"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
@@ -650,15 +638,11 @@
       <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L6" s="10"/>
       <c r="N6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O6" s="10"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
@@ -673,15 +657,11 @@
       <c r="G7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L7" s="10"/>
       <c r="N7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O7" s="10"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
@@ -696,15 +676,11 @@
       <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L8" s="10"/>
       <c r="N8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O8" s="10"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
@@ -719,15 +695,11 @@
       <c r="G9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L9" s="10"/>
       <c r="N9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O9" s="10"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
@@ -742,15 +714,11 @@
       <c r="G10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L10" s="10"/>
       <c r="N10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
@@ -765,15 +733,11 @@
       <c r="G11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="L11" s="10"/>
       <c r="N11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O11" s="11" t="s">
-        <v>11</v>
-      </c>
+      <c r="O11" s="10"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
